--- a/data/trans_dic/P41C_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P41C_R-Clase-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dificultades para tener un embarazo</t>
+          <t>Población con dificultades para tener un embarazo (tasa de respuesta: 87,29%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,26; 10,37</t>
+          <t>1,46; 10,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,25; 11,69</t>
+          <t>3,35; 11,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,22; 9,47</t>
+          <t>3,19; 8,68</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,22; 10,92</t>
+          <t>1,27; 11,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,65; 13,55</t>
+          <t>4,54; 14,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,73; 10,36</t>
+          <t>3,85; 10,3</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,91</t>
+          <t>0,0; 8,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,25</t>
+          <t>0,0; 13,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,11</t>
+          <t>0,0; 7,01</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,83; 8,3</t>
+          <t>2,04; 7,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,76; 4,8</t>
+          <t>0,87; 4,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,9; 5,55</t>
+          <t>1,81; 5,51</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,82</t>
+          <t>0,0; 6,97</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,99; 7,4</t>
+          <t>1,91; 7,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,4; 5,61</t>
+          <t>1,5; 5,51</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,03</t>
+          <t>0,0; 2,72</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,06</t>
+          <t>0,0; 1,81</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,06; 5,0</t>
+          <t>1,0; 4,77</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,0; 5,67</t>
+          <t>3,08; 5,7</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,96; 4,55</t>
+          <t>2,03; 4,64</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dificultades para tener un embarazo</t>
+          <t>Población con dificultades para tener un embarazo (tasa de respuesta: 87,29%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1411; 11585</t>
+          <t>1630; 11220</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3695; 13299</t>
+          <t>3807; 13364</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7259; 21349</t>
+          <t>7190; 19569</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1023; 9135</t>
+          <t>1061; 9928</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5021; 14637</t>
+          <t>4908; 15355</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7159; 19862</t>
+          <t>7387; 19756</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 30912</t>
+          <t>0; 30163</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4272</t>
+          <t>0; 4105</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 26778</t>
+          <t>0; 26401</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3767; 17036</t>
+          <t>4197; 15163</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1447; 9128</t>
+          <t>1660; 9490</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7511; 21937</t>
+          <t>7175; 21804</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 6467</t>
+          <t>0; 6607</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3021; 11247</t>
+          <t>2906; 10723</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3464; 13844</t>
+          <t>3702; 13591</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 2901</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 1671</t>
+          <t>0; 2239</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 2069</t>
+          <t>0; 1818</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>9129; 43024</t>
+          <t>8591; 41076</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>20292; 38361</t>
+          <t>20800; 38527</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>30163; 69959</t>
+          <t>31166; 71325</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P41C_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P41C_R-Clase-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,3%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,46; 10,04</t>
+          <t>1,64; 10,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,35; 11,75</t>
+          <t>3,04; 11,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,19; 8,68</t>
+          <t>3,07; 8,61</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,33%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,27; 11,87</t>
+          <t>1,23; 10,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,54; 14,21</t>
+          <t>4,31; 13,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,85; 10,3</t>
+          <t>3,64; 10,68</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,7</t>
+          <t>1,11; 18,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,69</t>
+          <t>0,0; 12,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,01</t>
+          <t>1,27; 15,37</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,04; 7,38</t>
+          <t>1,91; 7,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,87; 4,99</t>
+          <t>0,92; 4,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,81; 5,51</t>
+          <t>1,79; 5,49</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,97</t>
+          <t>0,0; 9,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,91; 7,06</t>
+          <t>2,23; 7,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,5; 5,51</t>
+          <t>1,75; 5,72</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,31%</t>
         </is>
       </c>
     </row>
@@ -827,12 +827,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,72</t>
+          <t>0,0; 2,34</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,81</t>
+          <t>0,0; 1,7</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,0; 4,77</t>
+          <t>2,29; 6,19</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,08; 5,7</t>
+          <t>2,93; 5,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,03; 4,64</t>
+          <t>3,01; 5,16</t>
         </is>
       </c>
     </row>
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5085</t>
+          <t>5124</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7540</t>
+          <t>7750</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12625</t>
+          <t>12874</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1630; 11220</t>
+          <t>1979; 12273</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3807; 13364</t>
+          <t>3707; 13647</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7190; 19569</t>
+          <t>7459; 20924</t>
         </is>
       </c>
     </row>
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>3416</t>
+          <t>3546</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>9156</t>
+          <t>9615</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12572</t>
+          <t>13161</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1061; 9928</t>
+          <t>1108; 9386</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4908; 15355</t>
+          <t>5071; 16038</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7387; 19756</t>
+          <t>7569; 22206</t>
         </is>
       </c>
     </row>
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5797</t>
+          <t>6362</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>741</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6479</t>
+          <t>7102</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 30163</t>
+          <t>1231; 20899</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4105</t>
+          <t>0; 4417</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 26401</t>
+          <t>1853; 22390</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>8665</t>
+          <t>9791</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>4370</t>
+          <t>4457</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13035</t>
+          <t>14248</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4197; 15163</t>
+          <t>4311; 17945</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1660; 9490</t>
+          <t>1955; 9344</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7175; 21804</t>
+          <t>7862; 24059</t>
         </is>
       </c>
     </row>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1453</t>
+          <t>1457</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5875</t>
+          <t>7331</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7328</t>
+          <t>8788</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1324,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 6607</t>
+          <t>0; 9943</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2906; 10723</t>
+          <t>3827; 13377</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3702; 13591</t>
+          <t>4905; 16028</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1379,12 +1379,12 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>345</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>345</t>
         </is>
       </c>
     </row>
@@ -1402,12 +1402,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 2239</t>
+          <t>0; 2153</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 1818</t>
+          <t>0; 1901</t>
         </is>
       </c>
     </row>
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>24416</t>
+          <t>26280</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>27976</t>
+          <t>30239</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>52392</t>
+          <t>56519</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>8591; 41076</t>
+          <t>15525; 41880</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>20800; 38527</t>
+          <t>21935; 41673</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>31166; 71325</t>
+          <t>42910; 73612</t>
         </is>
       </c>
     </row>
